--- a/notes/11-coding/programming_questions.xlsx
+++ b/notes/11-coding/programming_questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\pw-framework-qa-bank\notes\11-coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFA88E7-4F6C-419D-8964-3B648027EE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF12806-6B91-460D-A7E1-3AC809AEC256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="142">
   <si>
     <t>S.No</t>
   </si>
@@ -582,20 +582,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -927,12 +927,12 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
@@ -1004,12 +1004,12 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5" ht="50" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
@@ -1132,12 +1132,12 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
@@ -1158,12 +1158,12 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
@@ -1306,19 +1306,19 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="8"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
@@ -1336,7 +1336,7 @@
       <c r="E3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="9"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
@@ -1354,7 +1354,7 @@
       <c r="E4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       <c r="E5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
@@ -1392,7 +1392,7 @@
       <c r="E6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="9"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
@@ -1410,17 +1410,17 @@
       <c r="E7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="8"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
@@ -1438,7 +1438,9 @@
       <c r="E9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
@@ -1456,7 +1458,9 @@
       <c r="E10" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="9"/>
+      <c r="F10" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
@@ -1474,7 +1478,9 @@
       <c r="E11" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="9"/>
+      <c r="F11" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
@@ -1492,7 +1498,9 @@
       <c r="E12" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="9"/>
+      <c r="F12" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
@@ -1510,7 +1518,7 @@
       <c r="E13" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1530,17 +1538,19 @@
       <c r="E14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="9"/>
+      <c r="F14" s="8" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="8"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
@@ -1558,7 +1568,7 @@
       <c r="E16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="9"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
@@ -1576,7 +1586,7 @@
       <c r="E17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="9"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
@@ -1594,7 +1604,7 @@
       <c r="E18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="9"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
@@ -1612,7 +1622,7 @@
       <c r="E19" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F19" s="9"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
@@ -1630,17 +1640,17 @@
       <c r="E20" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="9"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="8"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
@@ -1658,17 +1668,17 @@
       <c r="E22" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="F22" s="9"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="8"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
@@ -1686,7 +1696,7 @@
       <c r="E24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="9"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
@@ -1704,7 +1714,7 @@
       <c r="E25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="9"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
@@ -1722,7 +1732,7 @@
       <c r="E26" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="9"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
@@ -1740,7 +1750,7 @@
       <c r="E27" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="9"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
@@ -1758,7 +1768,7 @@
       <c r="E28" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="9"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
@@ -1776,17 +1786,17 @@
       <c r="E29" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="9"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="8"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
@@ -1804,7 +1814,7 @@
       <c r="E31" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="9"/>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
@@ -1822,7 +1832,7 @@
       <c r="E32" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="9"/>
+      <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
@@ -1840,7 +1850,7 @@
       <c r="E33" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="9"/>
+      <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
@@ -1858,7 +1868,7 @@
       <c r="E34" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F34" s="9"/>
+      <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:6" ht="112.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
@@ -1876,7 +1886,7 @@
       <c r="E35" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F35" s="9"/>
+      <c r="F35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/notes/11-coding/programming_questions.xlsx
+++ b/notes/11-coding/programming_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\pw-framework-qa-bank\notes\11-coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF12806-6B91-460D-A7E1-3AC809AEC256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C1BDF4-77AE-4832-8B3C-DE6CD502097D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Strings" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="162">
   <si>
     <t>S.No</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>Hashing Based</t>
-  </si>
-  <si>
-    <t>Count the number of occurrences of each character in a string</t>
   </si>
   <si>
     <t>"aaaabbbbbccccddd"</t>
@@ -255,9 +252,6 @@
   </si>
   <si>
     <t>Left rotate an array by D places</t>
-  </si>
-  <si>
-    <t>arr = [1, 2, 3, 4, 5], D = 2</t>
   </si>
   <si>
     <t>[3, 4, 5, 1, 2]</t>
@@ -487,12 +481,79 @@
   <si>
     <t>md format</t>
   </si>
+  <si>
+    <t>Hashing Based + stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid Parenthesis </t>
+  </si>
+  <si>
+    <t>Valid Parentheses - LeetCode</t>
+  </si>
+  <si>
+    <t>Find all missing numbers from a given sorted array</t>
+  </si>
+  <si>
+    <t>[6,7,10,11,13]</t>
+  </si>
+  <si>
+    <t>8 9 12</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Find all missing numbers from a given sorted array - GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Find the Missing Number - GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>Count the number of occurrences of each character in a string or
+𝗖𝗼𝘂𝗻𝘁 𝗙𝗿𝗲𝗾𝘂𝗲𝗻𝗰𝘆 𝗼𝗳 𝗘𝗮𝗰𝗵 𝗖𝗵𝗮𝗿𝗮𝗰𝘁𝗲𝗿</t>
+  </si>
+  <si>
+    <t>Reverse alternate words in a sentence</t>
+  </si>
+  <si>
+    <t>Input: "I love my country"</t>
+  </si>
+  <si>
+    <t>Output: "I evol my yrtnuoc"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find longest word in sentence </t>
+  </si>
+  <si>
+    <t>Input: "Find the Longest Word in a Sentence"</t>
+  </si>
+  <si>
+    <t>Output: Sentence</t>
+  </si>
+  <si>
+    <t>Input: [1,2,3,4,5,6,7], Target = 8</t>
+  </si>
+  <si>
+    <t>Output: (1,7) (2,6) (3,5)</t>
+  </si>
+  <si>
+    <t>Find all pairs with given sum</t>
+  </si>
+  <si>
+    <t>use array methods sort()</t>
+  </si>
+  <si>
+    <t>Find all pairs with a given sum | Practice | GeeksforGeeks</t>
+  </si>
+  <si>
+    <t>arr = [1, 2, 3, 4, 5], D = 3</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,8 +577,33 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -539,6 +625,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,10 +659,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -592,12 +685,26 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -898,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -927,12 +1034,12 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
@@ -941,7 +1048,7 @@
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -958,7 +1065,7 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -975,7 +1082,7 @@
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="15" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -986,292 +1093,318 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="9" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" ht="50" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" ht="50" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="25" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="50" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="25" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" spans="1:5" ht="25" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>13</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
-        <v>13</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="4" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="25" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>14</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="25" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
-        <v>14</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="25" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
-        <v>15</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
-        <v>16</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
+        <v>15</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>16</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="25" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="4" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
+        <v>18</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
-        <v>18</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B7:E7"/>
     <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B19:E19"/>
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1280,17 +1413,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="6" width="36" customWidth="1"/>
+    <col min="3" max="3" width="37.54296875" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="7" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1304,23 +1438,27 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1328,17 +1466,20 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1346,37 +1487,41 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="G4" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1384,17 +1529,20 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1402,27 +1550,31 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1430,19 +1582,20 @@
         <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="G9" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1450,19 +1603,20 @@
         <v>18</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -1470,19 +1624,20 @@
         <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -1490,19 +1645,20 @@
         <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -1510,393 +1666,480 @@
         <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="G13" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="D15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="G15" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
+        <v>16</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
+        <v>17</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
-        <v>14</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" ht="25" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
-        <v>17</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="C26" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="9" t="s">
+      <c r="D26" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" ht="25" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
-        <v>18</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
+        <v>19</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" ht="25" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>19</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
+        <v>20</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="D28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" ht="25" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
-        <v>20</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" ht="25" x14ac:dyDescent="0.35">
-      <c r="A27" s="3">
-        <v>21</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>22</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" ht="25" x14ac:dyDescent="0.35">
-      <c r="A28" s="3">
-        <v>22</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
+        <v>23</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" ht="25" x14ac:dyDescent="0.35">
-      <c r="A29" s="3">
-        <v>23</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="E31" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="G31" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="A32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:7" ht="50" x14ac:dyDescent="0.35">
+      <c r="A34" s="3">
+        <v>24</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
-      <c r="B30" s="9" t="s">
+      <c r="D34" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" ht="50" x14ac:dyDescent="0.35">
-      <c r="A31" s="3">
-        <v>24</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="E34" s="4"/>
+      <c r="F34" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="3">
+        <v>25</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="3">
-        <v>25</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="E35" s="4"/>
+      <c r="F35" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="3">
+        <v>26</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="D36" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="3">
-        <v>26</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="G36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
+        <v>27</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="D37" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="3">
-        <v>27</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C34" s="4" t="s">
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="112.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="3">
+        <v>28</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="D38" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" ht="112.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="3">
-        <v>28</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F35" s="7"/>
+      <c r="G38" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B16:F16"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E14" r:id="rId1" display="https://leetcode.com/problems/valid-parentheses/description/" xr:uid="{E7F2E610-D926-452D-8493-4820873570BC}"/>
+    <hyperlink ref="E32" r:id="rId2" display="https://www.geeksforgeeks.org/dsa/find-all-missing-numbers-from-a-given-sorted-array/" xr:uid="{21B406A2-3956-4514-8B14-0CA5E2509F9C}"/>
+    <hyperlink ref="E31" r:id="rId3" display="https://www.geeksforgeeks.org/dsa/find-the-missing-number/" xr:uid="{D51E8FB4-55A5-47DE-B956-F1CF05C3C82E}"/>
+    <hyperlink ref="E21" r:id="rId4" display="https://www.geeksforgeeks.org/problems/find-all-pairs-whose-sum-is-x5808/1" xr:uid="{8DF32AEF-D7A7-428D-8765-7E0F8FBC345B}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/notes/11-coding/programming_questions.xlsx
+++ b/notes/11-coding/programming_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\pw-framework-qa-bank\notes\11-coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C1BDF4-77AE-4832-8B3C-DE6CD502097D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB13FE2-CB05-4E15-B4E6-3C763508B681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Strings" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="160">
   <si>
     <t>S.No</t>
   </si>
@@ -476,12 +476,6 @@
     *</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>md format</t>
-  </si>
-  <si>
     <t>Hashing Based + stack</t>
   </si>
   <si>
@@ -553,7 +547,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,8 +596,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,12 +620,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -663,7 +657,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -673,16 +667,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
@@ -695,11 +679,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1034,12 +1024,12 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
@@ -1048,7 +1038,7 @@
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -1065,7 +1055,7 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -1082,7 +1072,7 @@
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -1095,14 +1085,14 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1112,7 +1102,7 @@
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -1124,12 +1114,12 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" ht="50" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
@@ -1138,8 +1128,8 @@
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>149</v>
+      <c r="C9" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>19</v>
@@ -1155,7 +1145,7 @@
       <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -1172,7 +1162,7 @@
       <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1189,7 +1179,7 @@
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -1206,7 +1196,7 @@
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="9" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1223,7 +1213,7 @@
       <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="9" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -1236,14 +1226,14 @@
     <row r="15" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="25" x14ac:dyDescent="0.35">
@@ -1253,7 +1243,7 @@
       <c r="B16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="9" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -1265,12 +1255,12 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
@@ -1279,7 +1269,7 @@
       <c r="B18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -1291,12 +1281,12 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
@@ -1305,7 +1295,7 @@
       <c r="B20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -1322,10 +1312,10 @@
       <c r="B21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>48</v>
       </c>
       <c r="E21" s="4" t="s">
@@ -1339,7 +1329,7 @@
       <c r="B22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -1356,7 +1346,7 @@
       <c r="B23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="9" t="s">
         <v>53</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -1373,7 +1363,7 @@
       <c r="B24" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -1390,10 +1380,10 @@
       <c r="B25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E25" s="4" t="s">
@@ -1413,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1421,10 +1411,10 @@
     <col min="3" max="3" width="37.54296875" customWidth="1"/>
     <col min="4" max="4" width="23.453125" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="7" width="36" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1438,34 +1428,30 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -1475,18 +1461,15 @@
       <c r="F3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="9" t="s">
         <v>64</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -1496,92 +1479,79 @@
       <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="7" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>161</v>
+      <c r="D7" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1591,18 +1561,15 @@
       <c r="F9" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -1612,18 +1579,15 @@
       <c r="F10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1633,18 +1597,15 @@
       <c r="F11" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -1654,18 +1615,15 @@
       <c r="F12" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="9" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1675,34 +1633,28 @@
       <c r="F13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>142</v>
-      </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -1712,48 +1664,43 @@
       <c r="F15" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>93</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>13</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>95</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -1763,35 +1710,33 @@
       <c r="F18" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="8" t="s">
         <v>99</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -1801,33 +1746,31 @@
       <c r="F20" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="4"/>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>160</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="37.5" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>16</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="8" t="s">
         <v>101</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -1837,59 +1780,55 @@
       <c r="F22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+    </row>
+    <row r="24" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>17</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>106</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="12" t="s">
         <v>109</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -1899,16 +1838,15 @@
       <c r="F26" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="6" t="s">
         <v>112</v>
       </c>
       <c r="D27" s="4" t="s">
@@ -1918,16 +1856,15 @@
       <c r="F27" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="6" t="s">
         <v>115</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -1937,16 +1874,15 @@
       <c r="F28" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>117</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -1956,16 +1892,15 @@
       <c r="F29" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="6" t="s">
         <v>120</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -1975,88 +1910,79 @@
       <c r="F30" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>23</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="9" t="s">
         <v>122</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>148</v>
+      <c r="E31" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" spans="1:7" ht="50" x14ac:dyDescent="0.35">
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" ht="50" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>24</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="12" t="s">
         <v>126</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>127</v>
       </c>
       <c r="E34" s="4"/>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>25</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="12" t="s">
         <v>129</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -2066,16 +1992,15 @@
       <c r="F35" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G35" s="7"/>
-    </row>
-    <row r="36" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>26</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="12" t="s">
         <v>132</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -2085,16 +2010,15 @@
       <c r="F36" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G36" s="7"/>
-    </row>
-    <row r="37" spans="1:7" ht="62.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:6" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>27</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="8" t="s">
         <v>134</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -2104,16 +2028,15 @@
       <c r="F37" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G37" s="7"/>
-    </row>
-    <row r="38" spans="1:7" ht="112.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:6" ht="112.5" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>28</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="8" t="s">
         <v>136</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -2123,7 +2046,6 @@
       <c r="F38" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G38" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">
